--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5041.3</v>
+        <v>5013.74</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2520.95</v>
+        <v>2492.87</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2726</v>
+        <v>2722.53</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2676.15</v>
+        <v>2705.26</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2195.67</v>
+        <v>2219.55</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3529.09</v>
+        <v>3545.53</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>745.37</v>
+        <v>750.75</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7463.4</v>
+        <v>7517.21</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2414.93</v>
+        <v>2410.65</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2511.51</v>
+        <v>2507.62</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5456.45</v>
+        <v>5385.93</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8509.389999999999</v>
+        <v>8478.879999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3190.39</v>
+        <v>3177.02</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2925.6</v>
+        <v>2936.83</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2675.44</v>
+        <v>2687.57</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5413.8</v>
+        <v>5428.15</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1252.8</v>
+        <v>1254.41</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5181.29</v>
+        <v>5209.63</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>792.52</v>
+        <v>773.98</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7094.67</v>
+        <v>7002.98</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4601.33</v>
+        <v>4577.03</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2685.01</v>
+        <v>2668.18</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7771.6</v>
+        <v>7722.9</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1056.17</v>
+        <v>1063.09</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12297.01</v>
+        <v>12462.61</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3604.52</v>
+        <v>3695.64</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3638.93</v>
+        <v>3730.92</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2605.29</v>
+        <v>2671.15</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5496.16</v>
+        <v>5476.6</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4521.93</v>
+        <v>4505.83</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4284.19</v>
+        <v>4252.13</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>58875.2</v>
+        <v>59179.32</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>75093.94</v>
+        <v>75481.85000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>69040.14999999999</v>
+        <v>68749.05</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>28393.36</v>
+        <v>28273.64</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7603.18</v>
+        <v>7571.12</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5886.3</v>
+        <v>5861.48</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>15075.06</v>
+        <v>15116.44</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2868.91</v>
+        <v>2876.79</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1158.59</v>
+        <v>1166.65</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3304.04</v>
+        <v>3325.8</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7475.35</v>
+        <v>7524.58</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2205.32</v>
+        <v>2224.96</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16507.24</v>
+        <v>16388.98</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>77778.91</v>
+        <v>77221.71000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>77348.21000000001</v>
+        <v>76794.09</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1768.57</v>
+        <v>1755.9</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5771.09</v>
+        <v>5729.75</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6229.82</v>
+        <v>6220.65</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1683.77</v>
+        <v>1674.6</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2753.36</v>
+        <v>2738.37</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>18172.2</v>
+        <v>18189.72</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>9699.23</v>
+        <v>9723.1</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8925.139999999999</v>
+        <v>8810.24</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3351.03</v>
+        <v>3327.38</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7486.48</v>
+        <v>7622.21</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6668.8</v>
+        <v>6789.71</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1614</v>
+        <v>1609.55</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5855.88</v>
+        <v>5788.28</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8175.98</v>
+        <v>8123.61</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2115.82</v>
+        <v>2106.71</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3776.04</v>
+        <v>3721.42</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>6779.82</v>
+        <v>6633.95</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1074.34</v>
+        <v>1053.15</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2226.76</v>
+        <v>2168.12</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1579.38</v>
+        <v>1537.79</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5381.71</v>
+        <v>5239.99</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1694.05</v>
+        <v>1648.69</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2314.79</v>
+        <v>2334.43</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3204.21</v>
+        <v>3198.85</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1058.41</v>
+        <v>1056.64</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1142.94</v>
+        <v>1157.01</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>974.39</v>
+        <v>986.38</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1410.5</v>
+        <v>1427.86</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>13969.36</v>
+        <v>14313.15</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>12776.24</v>
+        <v>13090.67</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2572.48</v>
+        <v>2621.13</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4981.74</v>
+        <v>5075.95</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>896.5599999999999</v>
+        <v>913.51</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1455.61</v>
+        <v>1483.14</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1018.47</v>
+        <v>1037.74</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5441.16</v>
+        <v>5503.04</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6737.14</v>
+        <v>6797.83</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2535.57</v>
+        <v>2546.08</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2637.67</v>
+        <v>2648.6</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1911.17</v>
+        <v>1902.96</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3960.69</v>
+        <v>3926.9</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>12844.89</v>
+        <v>12735.33</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8130.61</v>
+        <v>8061.26</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>5436.12</v>
+        <v>5465.39</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>787.25</v>
+        <v>791.49</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>18998.33</v>
+        <v>19210.8</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>10363.73</v>
+        <v>10442.23</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1010.85</v>
+        <v>999.85</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4409.28</v>
+        <v>4399.28</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5394.01</v>
+        <v>5420.51</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1670.24</v>
+        <v>1678.45</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2192.45</v>
+        <v>2199.42</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1140.1</v>
+        <v>1143.73</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1573.93</v>
+        <v>1596.45</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7480.3</v>
+        <v>7550.46</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2210.57</v>
+        <v>2193.8</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3043.98</v>
+        <v>3000.78</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3242.94</v>
+        <v>3196.92</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1214.83</v>
+        <v>1198.14</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1781.99</v>
+        <v>1770.94</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>11962.99</v>
+        <v>11888.82</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>9492.370000000001</v>
+        <v>9535.48</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3880.11</v>
+        <v>3897.74</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2239.36</v>
+        <v>2272.7</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3590.76</v>
+        <v>3659.03</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2913.78</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1718.73</v>
+        <v>1751.4</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1170.35</v>
+        <v>1196.74</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1597.19</v>
+        <v>1633.21</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1683.06</v>
+        <v>1688.26</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3061.43</v>
+        <v>3070.89</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>26816.91</v>
+        <v>26292</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5388.29</v>
+        <v>5282.82</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4883.3</v>
+        <v>4782.94</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4484.44</v>
+        <v>4392.27</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1182.77</v>
+        <v>1158.46</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9842.42</v>
+        <v>9941.41</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>893.26</v>
+        <v>896.74</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3099.72</v>
+        <v>3084.02</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4541.36</v>
+        <v>4571.76</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>15971.57</v>
+        <v>16078.47</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>783.2</v>
+        <v>770.5599999999999</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2692.8</v>
+        <v>2649.63</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1040.48</v>
+        <v>1034.72</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2248.42</v>
+        <v>2235.95</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5228.63</v>
+        <v>5202.92</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3536.05</v>
+        <v>3518.66</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>20832.6</v>
+        <v>20730.17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>707409-131-CM25</t>
+          <t>5702-147-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRALES LTDA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.849.480-0</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5013.74</v>
+        <v>4213.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>707409-133-CM25</t>
+          <t>1151549-146-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRALES LTDA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.849.480-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2492.87</v>
+        <v>4752.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5360-410-CM25</t>
+          <t>1075963-21753-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>MULTI SAFE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>76.751.057-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2722.53</v>
+        <v>2217.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1346279-201-CM25</t>
+          <t>1272219-41-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,28 +752,28 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2705.26</v>
+        <v>3075.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3390-371-CM25</t>
+          <t>3348-99-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2219.55</v>
+        <v>2374.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>635-4825-CM25</t>
+          <t>2021-284-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3545.53</v>
+        <v>6211.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>720-541-CM25</t>
+          <t>1075963-24704-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,43 +935,43 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>750.75</v>
+        <v>3967.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1075963-55975-CM25</t>
+          <t>1173041-54-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7517.21</v>
+        <v>2223.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1075963-55981-CM25</t>
+          <t>1272219-56-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-8-LR25</t>
+          <t>2239-9-LR22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2410.65</v>
+        <v>3238.04</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5739-21-CM25</t>
+          <t>1075963-51901-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2507.62</v>
+        <v>5046.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079596-374-CM25</t>
+          <t>707409-131-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>SERVICIOS INTEGRALES LTDA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>76.849.480-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5385.93</v>
+        <v>5013.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1075963-56462-CM25</t>
+          <t>707409-133-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>SERVICIOS INTEGRALES LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.849.480-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8478.879999999999</v>
+        <v>2492.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4232-169-CM25</t>
+          <t>5360-410-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>Quality Rubber S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>76.097.502-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3177.02</v>
+        <v>2722.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>720-1120-CM25</t>
+          <t>3390-371-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2936.83</v>
+        <v>2219.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>635-4835-CM25</t>
+          <t>1346279-201-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2687.57</v>
+        <v>2705.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1075963-60710-CM25</t>
+          <t>635-4825-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5428.15</v>
+        <v>3545.53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5649-44-CM25</t>
+          <t>1075963-55975-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.979.030-8</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>BASTIAN IGNACIO</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.027.029-4</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1254.41</v>
+        <v>7517.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1075963-60889-CM25</t>
+          <t>720-541-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5209.63</v>
+        <v>750.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1075963-60712-CM25</t>
+          <t>1075963-55981-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>773.98</v>
+        <v>2410.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1075963-580-CM26</t>
+          <t>5739-21-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7002.98</v>
+        <v>2507.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1075963-1223-CM26</t>
+          <t>1079596-374-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4577.03</v>
+        <v>5385.93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1075963-1289-CM26</t>
+          <t>1075963-56462-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2668.18</v>
+        <v>8478.879999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2585-41-CM26</t>
+          <t>4232-169-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7722.9</v>
+        <v>3177.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1075963-1325-CM26</t>
+          <t>720-1120-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1063.09</v>
+        <v>2936.83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1093870-1-CM26</t>
+          <t>635-4835-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12462.61</v>
+        <v>2687.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4232-9-CM26</t>
+          <t>1075963-60710-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3695.64</v>
+        <v>5428.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1250331-4-CM26</t>
+          <t>5649-44-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.979.030-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>BASTIAN IGNACIO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>77.027.029-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3730.92</v>
+        <v>1254.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1250331-5-CM26</t>
+          <t>1075963-60889-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2671.15</v>
+        <v>5209.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4232-12-CM26</t>
+          <t>1075963-60712-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5476.6</v>
+        <v>773.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1075963-1765-CM26</t>
+          <t>1075963-580-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,17 +2293,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4505.83</v>
+        <v>7002.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>635-74-CM26</t>
+          <t>1075963-1223-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4252.13</v>
+        <v>4577.03</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1110404-60-CM26</t>
+          <t>1075963-1289-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>59179.32</v>
+        <v>2668.18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1110404-58-CM26</t>
+          <t>2585-41-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>75481.85000000001</v>
+        <v>7722.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1110404-63-CM26</t>
+          <t>1075963-1325-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>68749.05</v>
+        <v>1063.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1110404-64-CM26</t>
+          <t>1093870-1-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>28273.64</v>
+        <v>12462.61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1110404-65-CM26</t>
+          <t>1250331-5-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,12 +2659,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7571.12</v>
+        <v>2671.15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1110404-66-CM26</t>
+          <t>4232-9-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5861.48</v>
+        <v>3695.64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>635-109-CM26</t>
+          <t>1250331-4-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>15116.44</v>
+        <v>3730.92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1236-7-CM26</t>
+          <t>4232-12-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2876.79</v>
+        <v>5476.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5702-79-CM26</t>
+          <t>1075963-1765-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1166.65</v>
+        <v>4505.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1075963-2231-CM26</t>
+          <t>635-74-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3325.8</v>
+        <v>4252.13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5358-28-CM26</t>
+          <t>1110404-58-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7524.58</v>
+        <v>75481.85000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5358-29-CM26</t>
+          <t>1110404-60-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,22 +3091,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>2224.96</v>
+        <v>59179.32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1346279-21-CM26</t>
+          <t>1110404-65-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16388.98</v>
+        <v>7571.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1110404-84-CM26</t>
+          <t>1110404-63-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>77221.71000000001</v>
+        <v>68749.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1110404-85-CM26</t>
+          <t>1110404-64-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>76794.09</v>
+        <v>28273.64</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1075963-2435-CM26</t>
+          <t>1110404-66-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1755.9</v>
+        <v>5861.48</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1075963-2443-CM26</t>
+          <t>635-109-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5729.75</v>
+        <v>15116.44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3348-18-CM26</t>
+          <t>1236-7-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6220.65</v>
+        <v>2876.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3390-49-CM26</t>
+          <t>5702-79-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1674.6</v>
+        <v>1166.65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1075963-2605-CM26</t>
+          <t>1075963-2231-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2738.37</v>
+        <v>3325.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1075963-2920-CM26</t>
+          <t>5358-28-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,22 +3640,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>18189.72</v>
+        <v>7524.58</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1110404-145-CM26</t>
+          <t>5358-29-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3696,27 +3696,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>9723.1</v>
+        <v>2224.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2585-164-CM26</t>
+          <t>1346279-21-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>8810.24</v>
+        <v>16388.98</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1075963-3480-CM26</t>
+          <t>1075963-2443-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,17 +3818,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3327.38</v>
+        <v>5729.75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1317925-15-CM26</t>
+          <t>1110404-84-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7622.21</v>
+        <v>77221.71000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1317925-16-CM26</t>
+          <t>1110404-85-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6789.71</v>
+        <v>76794.09</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3459-49-CM26</t>
+          <t>1075963-2435-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1609.55</v>
+        <v>1755.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1075963-3883-CM26</t>
+          <t>3348-18-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5788.28</v>
+        <v>6220.65</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5702-206-CM26</t>
+          <t>3390-49-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>8123.61</v>
+        <v>1674.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2585-215-CM26</t>
+          <t>1075963-2605-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2106.71</v>
+        <v>2738.37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5042-9-CM26</t>
+          <t>1075963-2920-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3721.42</v>
+        <v>18189.72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5602-48-CM26</t>
+          <t>1110404-145-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>6633.95</v>
+        <v>9723.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>959257-11-CM26</t>
+          <t>2585-164-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.999.050-1</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1053.15</v>
+        <v>8810.24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2585-214-CM26</t>
+          <t>1075963-3480-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,27 +4428,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2168.12</v>
+        <v>3327.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5550-11-CM26</t>
+          <t>1317925-15-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1537.79</v>
+        <v>7622.21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3459-64-CM26</t>
+          <t>1317925-16-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>5239.99</v>
+        <v>6789.71</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1173457-11-CM26</t>
+          <t>3459-49-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1648.69</v>
+        <v>1609.55</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>720-38-CM26</t>
+          <t>1075963-3883-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2334.43</v>
+        <v>5788.28</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1272219-12-CM26</t>
+          <t>5702-206-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3198.85</v>
+        <v>8123.61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1272219-13-CM26</t>
+          <t>2585-215-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1056.64</v>
+        <v>2106.71</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3390-126-CM26</t>
+          <t>5042-9-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1157.01</v>
+        <v>3721.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3390-130-CM26</t>
+          <t>5602-48-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,12 +4916,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>986.38</v>
+        <v>6633.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3390-131-CM26</t>
+          <t>959257-11-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.999.050-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Ejército de Chile</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1427.86</v>
+        <v>1053.15</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1075963-5233-CM26</t>
+          <t>3459-64-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>14313.15</v>
+        <v>5239.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2021-77-CM26</t>
+          <t>2585-214-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>BIG MARKET SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.934.122-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>13090.67</v>
+        <v>2168.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1151549-88-CM26</t>
+          <t>5550-11-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>BASTIAN IGNACIO</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.027.029-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2621.13</v>
+        <v>1537.79</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1151549-89-CM26</t>
+          <t>1173457-11-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5075.95</v>
+        <v>1648.69</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5702-273-CM26</t>
+          <t>720-38-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>913.51</v>
+        <v>2334.43</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5702-274-CM26</t>
+          <t>1272219-12-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,22 +5348,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Economato del Complejo Penitenciario de Arica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1483.14</v>
+        <v>3198.85</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5484-93-CM26</t>
+          <t>1272219-13-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,22 +5409,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Economato del Complejo Penitenciario de Arica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1037.74</v>
+        <v>1056.64</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1075963-5466-CM26</t>
+          <t>3390-126-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5503.04</v>
+        <v>1157.01</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5360-103-CM26</t>
+          <t>3390-130-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,22 +5531,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6797.83</v>
+        <v>986.38</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>720-100-CM26</t>
+          <t>3390-131-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2546.08</v>
+        <v>1427.86</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2585-309-CM26</t>
+          <t>1075963-5233-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2648.6</v>
+        <v>14313.15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3459-108-CM26</t>
+          <t>2021-77-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.101.040-0</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Estado Mayor Conjunto</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y ALIMENTOS ICB FOOD SERVICE SPA</t>
+          <t>BIG MARKET SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>77.965.620-9</t>
+          <t>77.934.122-4</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1902.96</v>
+        <v>13090.67</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>720-123-CM26</t>
+          <t>5484-93-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,27 +5770,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3926.9</v>
+        <v>1037.74</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1075963-6178-CM26</t>
+          <t>5702-273-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,27 +5831,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>12735.33</v>
+        <v>913.51</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>707409-47-CM26</t>
+          <t>5702-274-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5892,27 +5892,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRALES LTDA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.849.480-0</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8061.26</v>
+        <v>1483.14</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>720-120-CM26</t>
+          <t>1151549-88-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>BASTIAN IGNACIO</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.027.029-4</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>5465.39</v>
+        <v>2621.13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1966-3-CM26</t>
+          <t>1151549-89-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>791.49</v>
+        <v>5075.95</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1110404-392-CM26</t>
+          <t>1075963-5466-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>19210.8</v>
+        <v>5503.04</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2585-357-CM26</t>
+          <t>5360-103-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>10442.23</v>
+        <v>6797.83</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1075963-6728-CM26</t>
+          <t>720-100-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>999.85</v>
+        <v>2546.08</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1075963-6784-CM26</t>
+          <t>2585-309-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4399.28</v>
+        <v>2648.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>635-604-CM26</t>
+          <t>3459-108-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>IMPORTADORA Y ALIMENTOS ICB FOOD SERVICE SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.965.620-9</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5420.51</v>
+        <v>1902.96</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5744-20-CM26</t>
+          <t>707409-47-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>SERVICIOS INTEGRALES LTDA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>76.849.480-0</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1678.45</v>
+        <v>8061.26</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1272219-20-CM26</t>
+          <t>720-123-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2199.42</v>
+        <v>3926.9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1075963-7121-CM26</t>
+          <t>1075963-6178-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1143.73</v>
+        <v>12735.33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3390-219-CM26</t>
+          <t>720-120-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1596.45</v>
+        <v>5465.39</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1347870-51-CM26</t>
+          <t>1966-3-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,27 +6624,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>7550.46</v>
+        <v>791.49</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1572-47-CM26</t>
+          <t>1110404-392-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2193.8</v>
+        <v>19210.8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3390-233-CM26</t>
+          <t>2585-357-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,27 +6746,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3000.78</v>
+        <v>10442.23</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1606-240-CM26</t>
+          <t>1075963-6728-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>3196.92</v>
+        <v>999.85</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>542429-43-CM26</t>
+          <t>1075963-6784-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1198.14</v>
+        <v>4399.28</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>635-741-CM26</t>
+          <t>5744-20-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6929,27 +6929,27 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVET SPA </t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.781.298-1</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1770.94</v>
+        <v>1678.45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1093870-6-CM26</t>
+          <t>635-604-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>11888.82</v>
+        <v>5420.51</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1079596-105-CM26</t>
+          <t>1075963-7121-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>9535.48</v>
+        <v>1143.73</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1079596-108-CM26</t>
+          <t>1272219-20-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>Economato del Complejo Penitenciario de Arica</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3897.74</v>
+        <v>2199.42</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5358-157-CM26</t>
+          <t>3390-219-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>2272.7</v>
+        <v>1596.45</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>720-141-CM26</t>
+          <t>1347870-51-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3659.03</v>
+        <v>7550.46</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>635-737-CM26</t>
+          <t>1572-47-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2969.17</v>
+        <v>2193.8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>5702-438-CM26</t>
+          <t>3390-233-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1751.4</v>
+        <v>3000.78</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1079596-111-CM26</t>
+          <t>1606-240-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1196.74</v>
+        <v>3196.92</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1075963-7938-CM26</t>
+          <t>542429-43-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1633.21</v>
+        <v>1198.14</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>635-823-CM26</t>
+          <t>635-741-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7544,12 +7544,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t xml:space="preserve">LIVET SPA </t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.781.298-1</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1688.26</v>
+        <v>1770.94</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>720-164-CM26</t>
+          <t>1093870-6-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>65.184.303-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,13 +7645,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>3070.89</v>
+        <v>11888.82</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2585-580-CM26</t>
+          <t>1079596-105-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7676,12 +7676,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>26292</v>
+        <v>9535.48</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1075963-8214-CM26</t>
+          <t>1079596-108-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>5282.82</v>
+        <v>3897.74</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3390-245-CM26</t>
+          <t>5358-157-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7788,22 +7788,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>4782.94</v>
+        <v>2272.7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3390-246-CM26</t>
+          <t>720-141-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4392.27</v>
+        <v>3659.03</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3390-257-CM26</t>
+          <t>635-737-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1158.46</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1075963-8631-CM26</t>
+          <t>5702-438-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>EQUILIBRIUM SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>9941.41</v>
+        <v>1751.4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>5739-11-CM26</t>
+          <t>1079596-111-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8027,27 +8027,27 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SECCIÓN COMPRAS XV ZONA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>896.74</v>
+        <v>1196.74</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1075963-9025-CM26</t>
+          <t>1075963-7938-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3084.02</v>
+        <v>1633.21</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>635-955-CM26</t>
+          <t>635-823-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>4571.76</v>
+        <v>1688.26</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>720-227-CM26</t>
+          <t>720-164-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8210,17 +8210,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>16078.47</v>
+        <v>3070.89</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>707409-72-CM26</t>
+          <t>2585-580-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRALES LTDA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>76.849.480-0</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>770.5599999999999</v>
+        <v>26292</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2021-145-CM26</t>
+          <t>1075963-8214-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2649.63</v>
+        <v>5282.82</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1272219-36-CM26</t>
+          <t>3390-245-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8393,27 +8393,27 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1034.72</v>
+        <v>4782.94</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1272219-37-CM26</t>
+          <t>3390-246-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8454,27 +8454,27 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2235.95</v>
+        <v>4392.27</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1075963-9655-CM26</t>
+          <t>3390-257-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5202.92</v>
+        <v>1158.46</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3459-192-CM26</t>
+          <t>1075963-8631-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8581,22 +8581,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3518.66</v>
+        <v>9941.41</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2585-750-CM26</t>
+          <t>5739-11-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>Comercial Agustin Limitada</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -8682,6 +8682,616 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
+        <v>896.74</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1075963-9025-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>tecnopapel s.a.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>3084.02</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>635-955-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>4571.76</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>720-227-CM26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Comercial Agustin Limitada</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>16078.47</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>707409-72-CM26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRALES LTDA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>76.849.480-0</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>770.5599999999999</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2021-145-CM26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>61.101.040-0</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Estado Mayor Conjunto</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>2649.63</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1272219-36-CM26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>61.979.880-5</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Economato del Complejo Penitenciario de Arica</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>16.770.707-6</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>1034.72</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1272219-37-CM26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>61.979.880-5</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Economato del Complejo Penitenciario de Arica</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>76.478.731-5</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>2235.95</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1075963-9655-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>5202.92</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>3459-192-CM26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA VYB</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>3518.66</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2585-750-CM26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>EQUILIBRIUM SPA</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
         <v>20730.17</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M262"/>
+  <dimension ref="A1:M275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1075963-6622-CM25</t>
+          <t>3459-22-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6303.27</v>
+        <v>6728.35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3459-22-CM25</t>
+          <t>1075963-6622-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6728.35</v>
+        <v>6303.27</v>
       </c>
     </row>
     <row r="25">
@@ -2161,7 +2161,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>720-68-CM25</t>
+          <t>720-81-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2128.09</v>
+        <v>17945.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>720-81-CM25</t>
+          <t>720-68-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>17945.14</v>
+        <v>2128.09</v>
       </c>
     </row>
     <row r="31">
@@ -2344,7 +2344,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2366-3729-CM25</t>
+          <t>1075963-7615-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3325.55</v>
+        <v>6657.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1075963-7615-CM25</t>
+          <t>2366-3729-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6657.62</v>
+        <v>3325.55</v>
       </c>
     </row>
     <row r="34">
@@ -2832,7 +2832,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5864-4-CM25</t>
+          <t>1075963-18619-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2492.42</v>
+        <v>3448.01</v>
       </c>
     </row>
     <row r="41">
@@ -2954,7 +2954,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1075963-18619-CM25</t>
+          <t>5864-4-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3448.01</v>
+        <v>2492.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>720-168-CM25</t>
+          <t>1075963-18673-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3011.54</v>
+        <v>3384.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1075963-18673-CM25</t>
+          <t>720-168-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3384.37</v>
+        <v>3011.54</v>
       </c>
     </row>
     <row r="45">
@@ -3564,7 +3564,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1075963-19406-CM25</t>
+          <t>3459-126-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2650.72</v>
+        <v>2578.31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3459-126-CM25</t>
+          <t>1075963-19406-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2578.31</v>
+        <v>2650.72</v>
       </c>
     </row>
     <row r="54">
@@ -4479,7 +4479,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5702-427-CM25</t>
+          <t>5702-428-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>MULTI SAFE SPA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.751.057-8</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2711.08</v>
+        <v>3820.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5702-428-CM25</t>
+          <t>5702-427-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>MULTI SAFE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>76.751.057-8</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3820.99</v>
+        <v>2711.08</v>
       </c>
     </row>
     <row r="69">
@@ -4784,7 +4784,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4232-70-CM25</t>
+          <t>1110404-719-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3716.03</v>
+        <v>35668.66</v>
       </c>
     </row>
     <row r="73">
@@ -4906,7 +4906,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1110404-719-CM25</t>
+          <t>4232-70-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>35668.66</v>
+        <v>3716.03</v>
       </c>
     </row>
     <row r="75">
@@ -6004,7 +6004,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1110404-1012-CM25</t>
+          <t>1110404-1040-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>70371.69</v>
+        <v>70134.62</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1110404-1016-CM25</t>
+          <t>1110404-1029-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>WINKLER LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>70112.94</v>
+        <v>70128.91</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1110404-1024-CM25</t>
+          <t>1110404-1012-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>70354.50999999999</v>
+        <v>70371.69</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1110404-1027-CM25</t>
+          <t>1110404-1016-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>70119.75999999999</v>
+        <v>70112.94</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1110404-1028-CM25</t>
+          <t>1110404-1024-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>70156.75999999999</v>
+        <v>70354.50999999999</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1110404-1029-CM25</t>
+          <t>1110404-1017-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>70128.91</v>
+        <v>70094.39</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1110404-1040-CM25</t>
+          <t>1110404-1028-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>70134.62</v>
+        <v>70156.75999999999</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1110404-1017-CM25</t>
+          <t>1110404-1027-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>70094.39</v>
+        <v>70119.75999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6919,7 +6919,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1173041-54-CM25</t>
+          <t>1075963-32320-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>70.456.600-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2223.11</v>
+        <v>8040.93</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1075963-32320-CM25</t>
+          <t>1173041-54-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.456.600-K</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>8040.93</v>
+        <v>2223.11</v>
       </c>
     </row>
     <row r="109">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>BASTIAN IGNACIO</t>
+          <t>Bastian Ignacio</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -9115,7 +9115,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1093870-1-CM26</t>
+          <t>4232-9-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>12462.61</v>
+        <v>3695.64</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1250331-5-CM26</t>
+          <t>1250331-4-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2671.15</v>
+        <v>3730.92</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1250331-4-CM26</t>
+          <t>1250331-5-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3730.92</v>
+        <v>2671.15</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4232-9-CM26</t>
+          <t>4232-12-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3695.64</v>
+        <v>5476.6</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4232-12-CM26</t>
+          <t>1075963-1765-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9379,17 +9379,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5476.6</v>
+        <v>4505.83</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1075963-1765-CM26</t>
+          <t>635-74-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9435,22 +9435,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4505.83</v>
+        <v>4252.13</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>635-74-CM26</t>
+          <t>1110404-58-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>4252.13</v>
+        <v>75481.85000000001</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1110404-58-CM26</t>
+          <t>1110404-60-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>75481.85000000001</v>
+        <v>59179.32</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1110404-60-CM26</t>
+          <t>1110404-63-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>59179.32</v>
+        <v>68749.05</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1110404-63-CM26</t>
+          <t>1110404-64-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>68749.05</v>
+        <v>28273.64</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1110404-64-CM26</t>
+          <t>1110404-65-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>28273.64</v>
+        <v>7571.12</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1110404-65-CM26</t>
+          <t>1110404-66-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>7571.12</v>
+        <v>5861.48</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1110404-66-CM26</t>
+          <t>1236-7-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5861.48</v>
+        <v>2876.79</v>
       </c>
     </row>
     <row r="156">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1236-7-CM26</t>
+          <t>5702-79-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,22 +9984,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2876.79</v>
+        <v>1166.65</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5702-79-CM26</t>
+          <t>1075963-2231-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10045,22 +10045,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1166.65</v>
+        <v>3325.8</v>
       </c>
     </row>
     <row r="159">
@@ -10152,7 +10152,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1075963-2231-CM26</t>
+          <t>5358-29-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10167,22 +10167,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3325.8</v>
+        <v>2224.96</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>5358-29-CM26</t>
+          <t>1075963-2443-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,22 +10228,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2224.96</v>
+        <v>5729.75</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1075963-2435-CM26</t>
+          <t>1110404-84-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1755.9</v>
+        <v>77221.71000000001</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1110404-84-CM26</t>
+          <t>1110404-85-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>77221.71000000001</v>
+        <v>76794.09</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1110404-85-CM26</t>
+          <t>1075963-2435-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10421,12 +10421,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>76794.09</v>
+        <v>1755.9</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1075963-2443-CM26</t>
+          <t>1346279-21-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>5729.75</v>
+        <v>16388.98</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1346279-21-CM26</t>
+          <t>3348-18-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>16388.98</v>
+        <v>6220.65</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3348-18-CM26</t>
+          <t>3390-49-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>6220.65</v>
+        <v>1674.6</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>3390-49-CM26</t>
+          <t>1075963-2605-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1674.6</v>
+        <v>2738.37</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1075963-2605-CM26</t>
+          <t>1075963-2920-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2738.37</v>
+        <v>18189.72</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1075963-2920-CM26</t>
+          <t>1110404-145-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>18189.72</v>
+        <v>9723.1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1110404-145-CM26</t>
+          <t>2585-164-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>9723.1</v>
+        <v>8810.24</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2585-164-CM26</t>
+          <t>1075963-3480-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10899,22 +10899,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>8810.24</v>
+        <v>3327.38</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1075963-3480-CM26</t>
+          <t>1317925-16-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3327.38</v>
+        <v>6789.71</v>
       </c>
     </row>
     <row r="174">
@@ -11067,7 +11067,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1317925-16-CM26</t>
+          <t>3459-49-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>6789.71</v>
+        <v>1609.55</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3459-49-CM26</t>
+          <t>1075963-3883-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11143,7 +11143,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1609.55</v>
+        <v>5788.28</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1075963-3883-CM26</t>
+          <t>5702-206-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>5788.28</v>
+        <v>8123.61</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5702-206-CM26</t>
+          <t>2585-215-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ADM SPA.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.909.208-9</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>8123.61</v>
+        <v>2106.71</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2585-215-CM26</t>
+          <t>5042-9-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>ADM SPA.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.909.208-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2106.71</v>
+        <v>3721.42</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5042-9-CM26</t>
+          <t>5602-48-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3721.42</v>
+        <v>6633.95</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>5602-48-CM26</t>
+          <t>959257-11-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.999.050-1</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>6633.95</v>
+        <v>1053.15</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>959257-11-CM26</t>
+          <t>2585-214-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.999.050-1</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Ejército de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1053.15</v>
+        <v>2168.12</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5550-11-CM26</t>
+          <t>3459-64-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1537.79</v>
+        <v>5239.99</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2585-214-CM26</t>
+          <t>1173457-11-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>75.554.600-3</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2168.12</v>
+        <v>1648.69</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3459-64-CM26</t>
+          <t>720-38-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11702,12 +11702,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5239.99</v>
+        <v>2334.43</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1173457-11-CM26</t>
+          <t>1272219-12-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>75.554.600-3</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Centro Educación y Trabajo Régimen Cerrado CP Aric</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1648.69</v>
+        <v>3198.85</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>720-38-CM26</t>
+          <t>1272219-13-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2334.43</v>
+        <v>1056.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1272219-12-CM26</t>
+          <t>3390-126-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3198.85</v>
+        <v>1157.01</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1272219-13-CM26</t>
+          <t>3390-130-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1056.64</v>
+        <v>986.38</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3390-126-CM26</t>
+          <t>3390-131-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1157.01</v>
+        <v>1427.86</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3390-130-CM26</t>
+          <t>837-219-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>986.38</v>
+        <v>966.72</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3390-131-CM26</t>
+          <t>837-218-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.176.425-k</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1427.86</v>
+        <v>1417.83</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2021-77-CM26</t>
+          <t>837-215-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>BIG MARKET SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>77.934.122-4</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>13090.67</v>
+        <v>1262.08</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1075963-5233-CM26</t>
+          <t>837-217-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,13 +12281,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>14313.15</v>
+        <v>1127.78</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1151549-88-CM26</t>
+          <t>837-214-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12302,22 +12302,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12327,12 +12327,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>BASTIAN IGNACIO</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>77.027.029-4</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2621.13</v>
+        <v>1147.28</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1151549-89-CM26</t>
+          <t>837-222-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5075.95</v>
+        <v>1006.71</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>5702-273-CM26</t>
+          <t>837-224-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>913.51</v>
+        <v>815.71</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5702-274-CM26</t>
+          <t>837-226-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>78.209.441-6</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1483.14</v>
+        <v>870.09</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5484-93-CM26</t>
+          <t>1075963-5233-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12546,22 +12546,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1037.74</v>
+        <v>14313.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1075963-5466-CM26</t>
+          <t>1151549-88-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12607,22 +12607,22 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Bastian Ignacio</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.027.029-4</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>5503.04</v>
+        <v>2621.13</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>5360-103-CM26</t>
+          <t>1151549-89-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>6797.83</v>
+        <v>5075.95</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2585-309-CM26</t>
+          <t>5702-273-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12729,22 +12729,22 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2648.6</v>
+        <v>913.51</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>720-100-CM26</t>
+          <t>5702-274-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12790,22 +12790,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2546.08</v>
+        <v>1483.14</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3459-108-CM26</t>
+          <t>5484-93-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12851,22 +12851,22 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y ALIMENTOS ICB FOOD SERVICE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.965.620-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1902.96</v>
+        <v>1037.74</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>720-123-CM26</t>
+          <t>1075963-5466-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12907,12 +12907,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3926.9</v>
+        <v>5503.04</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1075963-6178-CM26</t>
+          <t>5360-103-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12968,27 +12968,27 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>12735.33</v>
+        <v>6797.83</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>707409-47-CM26</t>
+          <t>2585-309-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13044,12 +13044,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRALES LTDA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.849.480-0</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13074,13 +13074,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>8061.26</v>
+        <v>2648.6</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>720-120-CM26</t>
+          <t>720-100-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5465.39</v>
+        <v>2546.08</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1966-3-CM26</t>
+          <t>3459-108-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13151,27 +13151,27 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>IMPORTADORA Y ALIMENTOS ICB FOOD SERVICE SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>77.965.620-9</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>791.49</v>
+        <v>1902.96</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1110404-392-CM26</t>
+          <t>720-123-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>19210.8</v>
+        <v>3926.9</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2585-357-CM26</t>
+          <t>1075963-6178-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13278,22 +13278,22 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>10442.23</v>
+        <v>12735.33</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1075963-6728-CM26</t>
+          <t>707409-47-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SERVICIOS INTEGRALES LTDA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.849.480-0</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>999.85</v>
+        <v>8061.26</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1075963-6784-CM26</t>
+          <t>720-120-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13425,12 +13425,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4399.28</v>
+        <v>5465.39</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>635-604-CM26</t>
+          <t>1966-3-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13461,22 +13461,22 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>5420.51</v>
+        <v>791.49</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5744-20-CM26</t>
+          <t>1110404-392-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1678.45</v>
+        <v>19210.8</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1272219-20-CM26</t>
+          <t>2585-357-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13583,22 +13583,22 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2199.42</v>
+        <v>10442.23</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1075963-7121-CM26</t>
+          <t>1075963-6728-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1143.73</v>
+        <v>999.85</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3390-219-CM26</t>
+          <t>1075963-6784-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13700,12 +13700,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -13715,12 +13715,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1596.45</v>
+        <v>4399.28</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1347870-51-CM26</t>
+          <t>635-604-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13761,12 +13761,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7550.46</v>
+        <v>5420.51</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1572-47-CM26</t>
+          <t>5744-20-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13822,12 +13822,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2193.8</v>
+        <v>1678.45</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3390-233-CM26</t>
+          <t>1272219-20-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>SOSEG SPA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.897.534-5</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3000.78</v>
+        <v>2199.42</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1606-240-CM26</t>
+          <t>1075963-7121-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -13959,12 +13959,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13989,13 +13989,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>3196.92</v>
+        <v>1143.73</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>542429-43-CM26</t>
+          <t>3390-219-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14035,12 +14035,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K223" t="inlineStr"/>
@@ -14050,13 +14050,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1198.14</v>
+        <v>1596.45</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>635-741-CM26</t>
+          <t>1347870-51-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14071,22 +14071,22 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIVET SPA </t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.781.298-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14111,13 +14111,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1770.94</v>
+        <v>7550.46</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1093870-6-CM26</t>
+          <t>1572-47-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -14142,12 +14142,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>65.184.303-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EDUCACION SUPERIOR</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K225" t="inlineStr"/>
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>11888.82</v>
+        <v>2193.8</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1079596-105-CM26</t>
+          <t>3390-233-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -14203,12 +14203,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOSEG SPA</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.897.534-5</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>9535.48</v>
+        <v>3000.78</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1079596-108-CM26</t>
+          <t>1606-240-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3897.74</v>
+        <v>3196.92</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>5358-157-CM26</t>
+          <t>635-741-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>LIVET SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>76.781.298-1</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2272.7</v>
+        <v>1770.94</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>720-141-CM26</t>
+          <t>1079596-105-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -14386,12 +14386,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14401,12 +14401,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3659.03</v>
+        <v>9535.48</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>635-737-CM26</t>
+          <t>1079596-108-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -14447,12 +14447,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>2969.17</v>
+        <v>3897.74</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>5702-438-CM26</t>
+          <t>720-141-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14538,13 +14538,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1751.4</v>
+        <v>3659.03</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1075963-7938-CM26</t>
+          <t>635-737-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14559,7 +14559,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -14569,12 +14569,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14584,12 +14584,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1633.21</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1079596-111-CM26</t>
+          <t>5702-438-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -14630,12 +14630,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K233" t="inlineStr"/>
@@ -14660,13 +14660,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1196.74</v>
+        <v>1751.4</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>720-164-CM26</t>
+          <t>1079596-111-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -14691,12 +14691,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3070.89</v>
+        <v>1196.74</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>635-823-CM26</t>
+          <t>1075963-7938-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -14752,12 +14752,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14767,12 +14767,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -14782,13 +14782,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1688.26</v>
+        <v>1633.21</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2585-580-CM26</t>
+          <t>720-164-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -14843,13 +14843,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>26292</v>
+        <v>3070.89</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1075963-8214-CM26</t>
+          <t>635-823-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -14904,13 +14904,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>5282.82</v>
+        <v>1688.26</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3390-245-CM26</t>
+          <t>2585-580-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14935,12 +14935,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -14965,13 +14965,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>4782.94</v>
+        <v>26292</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3390-246-CM26</t>
+          <t>1075963-8214-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14996,12 +14996,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15011,12 +15011,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15026,13 +15026,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>4392.27</v>
+        <v>5282.82</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3390-257-CM26</t>
+          <t>837-416-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15087,13 +15087,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1158.46</v>
+        <v>3568.04</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1075963-8631-CM26</t>
+          <t>3390-257-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15103,12 +15103,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15148,13 +15148,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>9941.41</v>
+        <v>1158.46</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5739-11-CM26</t>
+          <t>3390-246-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15164,27 +15164,27 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15209,13 +15209,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>896.74</v>
+        <v>4392.27</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1075963-9025-CM26</t>
+          <t>3390-245-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15225,12 +15225,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15270,13 +15270,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>3084.02</v>
+        <v>4782.94</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>635-955-CM26</t>
+          <t>1075963-8631-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -15301,12 +15301,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15316,12 +15316,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K244" t="inlineStr"/>
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4571.76</v>
+        <v>9941.41</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>720-227-CM26</t>
+          <t>5739-11-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -15392,13 +15392,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>16078.47</v>
+        <v>896.74</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>707409-72-CM26</t>
+          <t>1075963-9025-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -15423,12 +15423,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15438,12 +15438,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRALES LTDA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.849.480-0</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K246" t="inlineStr"/>
@@ -15453,13 +15453,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>770.5599999999999</v>
+        <v>3084.02</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2021-145-CM26</t>
+          <t>635-955-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.101.040-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Estado Mayor Conjunto</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K247" t="inlineStr"/>
@@ -15514,13 +15514,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2649.63</v>
+        <v>4571.76</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1272219-36-CM26</t>
+          <t>720-227-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15535,22 +15535,22 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15560,12 +15560,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K248" t="inlineStr"/>
@@ -15575,13 +15575,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1034.72</v>
+        <v>16078.47</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1272219-37-CM26</t>
+          <t>707409-72-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15596,22 +15596,22 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15621,12 +15621,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>SERVICIOS INTEGRALES LTDA</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>76.849.480-0</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15636,13 +15636,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2235.95</v>
+        <v>770.5599999999999</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2585-750-CM26</t>
+          <t>1272219-36-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -15667,12 +15667,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM SPA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -15697,13 +15697,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>20730.17</v>
+        <v>1034.72</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1075963-9655-CM26</t>
+          <t>1272219-37-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15718,22 +15718,22 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>5202.92</v>
+        <v>2235.95</v>
       </c>
     </row>
     <row r="252">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15825,7 +15825,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3459-195-CM26</t>
+          <t>1075963-9655-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -15880,13 +15880,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2535.16</v>
+        <v>5202.92</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>635-1033-CM26</t>
+          <t>2585-750-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15896,27 +15896,27 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15926,12 +15926,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K254" t="inlineStr"/>
@@ -15941,13 +15941,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3946.26</v>
+        <v>20730.17</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1075963-9996-CM26</t>
+          <t>3459-195-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15962,22 +15962,22 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -15987,12 +15987,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K255" t="inlineStr"/>
@@ -16002,13 +16002,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>6851.3</v>
+        <v>2535.16</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1347870-117-CM26</t>
+          <t>635-1033-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>6654.94</v>
+        <v>3946.26</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1347870-118-CM26</t>
+          <t>1075963-9996-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16084,22 +16084,22 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16109,12 +16109,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16124,13 +16124,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>6654.94</v>
+        <v>6851.3</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1110404-819-CM26</t>
+          <t>1347870-118-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -16155,12 +16155,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16170,12 +16170,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16185,13 +16185,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>5992.32</v>
+        <v>6654.94</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>720-253-CM26</t>
+          <t>1347870-117-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>851.02</v>
+        <v>6654.94</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1075963-10940-CM26</t>
+          <t>1110404-819-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16267,22 +16267,22 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16292,12 +16292,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>5237.66</v>
+        <v>5992.32</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1075963-10955-CM26</t>
+          <t>720-253-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16353,12 +16353,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K261" t="inlineStr"/>
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>4922.27</v>
+        <v>851.02</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>635-1192-CM26</t>
+          <t>1075963-10940-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -16399,12 +16399,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K262" t="inlineStr"/>
@@ -16429,7 +16429,800 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
+        <v>5237.66</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>1075963-10955-CM26</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>4922.27</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>635-1192-CM26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="n">
         <v>2717.37</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>1075963-11634-CM26</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>tecnopapel s.a.</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="n">
+        <v>8234.219999999999</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>3348-96-CM26</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>61.101.082-6</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="n">
+        <v>9126.27</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1272219-53-CM26</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>61.979.880-5</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>76.478.731-5</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>1478.93</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>3459-242-CM26</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA VYB</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="n">
+        <v>1995.28</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1272219-56-CM26</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>61.979.880-5</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>16.770.707-6</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>1732.37</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>720-280-CM26</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="n">
+        <v>758.37</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>959257-50-CM26</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>61.999.050-1</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="n">
+        <v>1282.27</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1075963-12438-CM26</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>tecnopapel s.a.</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="n">
+        <v>5040.25</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1173457-42-CM26</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>75.554.600-3</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="n">
+        <v>1461.55</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>3459-254-CM26</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA VYB</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="n">
+        <v>886.09</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>1075963-12750-CM26</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="n">
+        <v>4048.99</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
@@ -1111,7 +1111,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1176,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1241,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1550,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1676,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1802,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1867,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1932,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2180,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2550,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2737,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2924,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2989,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3054,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3241,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3306,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3615,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3863,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4172,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4298,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4424,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4550,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4798,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4924,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5050,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5237,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5302,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5428,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5615,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5680,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5806,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5871,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5936,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6001,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6127,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6314,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6379,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6444,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6875,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7001,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7249,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7314,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7379,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7566,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7631,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8062,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8127,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8253,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8379,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8444,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8692,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8818,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9005,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9131,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9257,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9322,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9387,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9574,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9822,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9948,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10135,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10261,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10509,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10635,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10822,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10887,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11257,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11322,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11452,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11517,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11582,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11647,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11834,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11899,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11964,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12090,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12216,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12281,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12712,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12777,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12842,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13029,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13155,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13220,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13285,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13350,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13842,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13907,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +13972,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14037,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14102,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14472,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14537,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14785,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14850,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14915,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15346,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15411,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15476,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15541,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15606,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15671,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15919,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16289,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16476,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16602,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +16667,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16793,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +16919,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +16984,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17110,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17419,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17545,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +17671,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
@@ -1306,7 +1306,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1489,7 +1493,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2119,7 +2127,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2306,7 +2318,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2367,7 +2383,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2489,7 +2509,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2676,7 +2700,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3432,7 +3460,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3554,7 +3586,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3989,7 +4025,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4111,7 +4151,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4863,7 +4907,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5176,7 +5224,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6253,7 +6305,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6631,7 +6687,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6814,7 +6874,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7066,7 +7130,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7444,7 +7512,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8192,7 +8264,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8757,7 +8833,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9700,7 +9780,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10013,7 +10097,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10288,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12029,7 +12121,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13598,7 +13694,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13781,7 +13881,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14167,7 +14271,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14663,7 +14771,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14980,7 +15092,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15224,7 +15340,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15285,7 +15405,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15797,7 +15921,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15984,7 +16112,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17358,7 +17490,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M275"/>
+  <dimension ref="A1:M285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1110404-5-CM25</t>
+          <t>2366-19-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,28 +615,32 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>66379.78999999999</v>
+        <v>24874.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1110404-6-CM25</t>
+          <t>1075963-697-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -661,12 +665,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,28 +680,32 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>64819.05</v>
+        <v>4346.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1110404-7-CM25</t>
+          <t>1110404-11-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -752,13 +760,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>64898.1</v>
+        <v>19455.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1110404-8-CM25</t>
+          <t>1110404-10-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>52571.11</v>
+        <v>51831.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1110404-9-CM25</t>
+          <t>1075963-689-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,17 +847,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +867,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JOHANA JESSICA ROJAS BOUFFANAIS</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.297.949-2</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +882,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>33874.44</v>
+        <v>7221.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1110404-10-CM25</t>
+          <t>1110404-8-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,13 +943,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>51831.95</v>
+        <v>52571.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1110404-11-CM25</t>
+          <t>1110404-7-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -996,13 +1004,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>19455.54</v>
+        <v>64898.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1075963-689-CM25</t>
+          <t>1110404-6-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1030,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1050,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1065,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7221.17</v>
+        <v>64819.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1075963-697-CM25</t>
+          <t>1110404-5-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1088,12 +1096,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,32 +1111,28 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>77.038.841-4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4346.69</v>
+        <v>66379.78999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2366-19-CM25</t>
+          <t>1110404-9-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1153,12 +1157,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,26 +1172,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>JOHANA JESSICA ROJAS BOUFFANAIS</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>11.297.949-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>24874.64</v>
+        <v>33874.44</v>
       </c>
     </row>
     <row r="13">
@@ -1445,7 +1445,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1346279-29-CM25</t>
+          <t>1346279-19-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3426.22</v>
+        <v>7470.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1346279-19-CM25</t>
+          <t>1346279-29-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7470.31</v>
+        <v>3426.22</v>
       </c>
     </row>
     <row r="19">
@@ -1827,7 +1827,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3459-22-CM25</t>
+          <t>1075963-6622-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1886,13 +1886,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6728.35</v>
+        <v>6303.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1075963-6622-CM25</t>
+          <t>3459-22-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6303.27</v>
+        <v>6728.35</v>
       </c>
     </row>
     <row r="25">
@@ -2400,7 +2400,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1075963-7615-CM25</t>
+          <t>2366-3729-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2440,28 +2440,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6657.62</v>
+        <v>3325.55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2366-3729-CM25</t>
+          <t>1075963-7615-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2486,12 +2490,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2501,26 +2505,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3325.55</v>
+        <v>6657.62</v>
       </c>
     </row>
     <row r="34">
@@ -2904,7 +2904,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1075963-18619-CM25</t>
+          <t>5864-4-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2924,17 +2924,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3448.01</v>
+        <v>2492.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5702-243-CM25</t>
+          <t>1075963-18619-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3028,13 +3028,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2346.61</v>
+        <v>3448.01</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5864-4-CM25</t>
+          <t>5702-243-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3054,17 +3054,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3093,13 +3093,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2492.42</v>
+        <v>2346.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1075963-18673-CM25</t>
+          <t>720-168-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3384.37</v>
+        <v>3011.54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>720-168-CM25</t>
+          <t>1075963-18673-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3011.54</v>
+        <v>3384.37</v>
       </c>
     </row>
     <row r="45">
@@ -4611,7 +4611,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5702-428-CM25</t>
+          <t>5702-427-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>MULTI SAFE SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
+          <t>76.751.057-8</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4666,13 +4666,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3820.99</v>
+        <v>2711.08</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5702-427-CM25</t>
+          <t>5702-428-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>MULTI SAFE SPA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.751.057-8</t>
+          <t>77.038.841-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2711.08</v>
+        <v>3820.99</v>
       </c>
     </row>
     <row r="69">
@@ -5558,7 +5558,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1075963-23008-CM25</t>
+          <t>1347870-88-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5583,12 +5583,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5598,28 +5598,32 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5452.91</v>
+        <v>5776.31</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1347870-88-CM25</t>
+          <t>3459-212-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5644,12 +5648,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5659,26 +5663,22 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA PRANDELLI LIMITADA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.295.342-0</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5776.31</v>
+        <v>5017.66</v>
       </c>
     </row>
     <row r="84">
@@ -5749,7 +5749,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3459-212-CM25</t>
+          <t>1075963-23008-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA PRANDELLI LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.295.342-0</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5017.66</v>
+        <v>5452.91</v>
       </c>
     </row>
     <row r="86">
@@ -6070,7 +6070,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1075963-23769-CM25</t>
+          <t>3348-99-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.101.082-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6110,28 +6110,32 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8032.11</v>
+        <v>2374.49</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3348-99-CM25</t>
+          <t>1075963-23769-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6156,12 +6160,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.101.082-6</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6171,32 +6175,28 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2374.49</v>
+        <v>8032.11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1110404-1040-CM25</t>
+          <t>1110404-1024-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6236,22 +6236,26 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>70134.62</v>
+        <v>70354.50999999999</v>
       </c>
     </row>
     <row r="93">
@@ -6322,7 +6326,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1110404-1012-CM25</t>
+          <t>1110404-1040-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6362,32 +6366,28 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.038.841-4</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>70371.69</v>
+        <v>70134.62</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1110404-1016-CM25</t>
+          <t>1110404-1027-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>WINKLER LIMITADA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>79.722.860-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>70112.94</v>
+        <v>70119.75999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1110404-1024-CM25</t>
+          <t>1110404-1016-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6492,17 +6492,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>WINKLER LIMITADA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>79.722.860-5</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6511,13 +6511,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>70354.50999999999</v>
+        <v>70112.94</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1110404-1017-CM25</t>
+          <t>1110404-1028-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6572,13 +6572,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>70094.39</v>
+        <v>70156.75999999999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1110404-1028-CM25</t>
+          <t>1110404-1012-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6618,28 +6618,32 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>70156.75999999999</v>
+        <v>70371.69</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1110404-1027-CM25</t>
+          <t>1110404-1017-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6679,26 +6683,22 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>70119.75999999999</v>
+        <v>70094.39</v>
       </c>
     </row>
     <row r="100">
@@ -9419,7 +9419,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4232-9-CM26</t>
+          <t>1250331-5-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9459,32 +9459,28 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>16.770.707-6</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3695.64</v>
+        <v>2671.15</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1250331-4-CM26</t>
+          <t>4232-9-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9509,12 +9505,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9524,28 +9520,32 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+          <t>77.823.479-3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3730.92</v>
+        <v>3695.64</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1250331-5-CM26</t>
+          <t>1250331-4-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2671.15</v>
+        <v>3730.92</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4232-12-CM26</t>
+          <t>1075963-1765-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9626,17 +9626,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9646,32 +9646,28 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5476.6</v>
+        <v>4505.83</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1075963-1765-CM26</t>
+          <t>4232-12-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9691,17 +9687,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9711,22 +9707,26 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4505.83</v>
+        <v>5476.6</v>
       </c>
     </row>
     <row r="148">
@@ -9797,7 +9797,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1110404-58-CM26</t>
+          <t>1110404-60-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9837,28 +9837,32 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>75481.85000000001</v>
+        <v>59179.32</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1110404-60-CM26</t>
+          <t>1110404-58-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9898,32 +9902,28 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.038.841-4</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>59179.32</v>
+        <v>75481.85000000001</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1110404-63-CM26</t>
+          <t>1110404-66-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>68749.05</v>
+        <v>5861.48</v>
       </c>
     </row>
     <row r="152">
@@ -10049,7 +10049,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1110404-65-CM26</t>
+          <t>1110404-63-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10089,32 +10089,28 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>9.454.737-7</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>7571.12</v>
+        <v>68749.05</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1110404-66-CM26</t>
+          <t>1110404-65-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10154,22 +10150,26 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>5861.48</v>
+        <v>7571.12</v>
       </c>
     </row>
     <row r="155">
@@ -10370,7 +10370,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1075963-2231-CM26</t>
+          <t>5358-28-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10390,17 +10390,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10425,13 +10425,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>3325.8</v>
+        <v>7524.58</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5358-28-CM26</t>
+          <t>1075963-2231-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10451,17 +10451,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7524.58</v>
+        <v>3325.8</v>
       </c>
     </row>
     <row r="160">
@@ -10553,7 +10553,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1075963-2443-CM26</t>
+          <t>1110404-84-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10593,32 +10593,28 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL ROYA WOLF SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>77.038.841-4</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>5729.75</v>
+        <v>77221.71000000001</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1110404-84-CM26</t>
+          <t>1110404-85-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10658,28 +10654,32 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIAL ROYA WOLF SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.038.841-4</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>77221.71000000001</v>
+        <v>76794.09</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1110404-85-CM26</t>
+          <t>1075963-2435-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10704,12 +10704,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10719,32 +10719,28 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>76794.09</v>
+        <v>1755.9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1075963-2435-CM26</t>
+          <t>1346279-21-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10769,12 +10765,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10784,12 +10780,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.475.342-9</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10799,13 +10795,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1755.9</v>
+        <v>16388.98</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1346279-21-CM26</t>
+          <t>1075963-2443-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10830,12 +10826,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10845,22 +10841,26 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>16388.98</v>
+        <v>5729.75</v>
       </c>
     </row>
     <row r="166">
@@ -11878,7 +11878,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2585-214-CM26</t>
+          <t>3459-64-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11903,12 +11903,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11918,17 +11918,17 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11937,13 +11937,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2168.12</v>
+        <v>5239.99</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3459-64-CM26</t>
+          <t>2585-214-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11983,17 +11983,17 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -12002,7 +12002,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>5239.99</v>
+        <v>2168.12</v>
       </c>
     </row>
     <row r="184">
@@ -12138,7 +12138,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1272219-12-CM26</t>
+          <t>1272219-13-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12178,32 +12178,28 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>16.770.707-6</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3198.85</v>
+        <v>1056.64</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1272219-13-CM26</t>
+          <t>1272219-12-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12243,28 +12239,32 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1056.64</v>
+        <v>3198.85</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3390-126-CM26</t>
+          <t>3390-131-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12304,26 +12304,22 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1157.01</v>
+        <v>1427.86</v>
       </c>
     </row>
     <row r="189">
@@ -12394,7 +12390,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3390-131-CM26</t>
+          <t>3390-126-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12434,28 +12430,32 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1427.86</v>
+        <v>1157.01</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>837-219-CM26</t>
+          <t>837-217-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12510,13 +12510,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>966.72</v>
+        <v>1127.78</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>837-218-CM26</t>
+          <t>837-215-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12556,12 +12556,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12571,13 +12571,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1417.83</v>
+        <v>1262.08</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>837-215-CM26</t>
+          <t>837-219-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12632,13 +12632,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1262.08</v>
+        <v>966.72</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>837-217-CM26</t>
+          <t>837-218-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.176.425-k</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12693,7 +12693,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1127.78</v>
+        <v>1417.83</v>
       </c>
     </row>
     <row r="195">
@@ -13463,7 +13463,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2585-309-CM26</t>
+          <t>720-100-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13518,13 +13518,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2648.6</v>
+        <v>2546.08</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>720-100-CM26</t>
+          <t>2585-309-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2546.08</v>
+        <v>2648.6</v>
       </c>
     </row>
     <row r="209">
@@ -13646,7 +13646,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>720-123-CM26</t>
+          <t>707409-47-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13671,12 +13671,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13686,26 +13686,22 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>SERVICIOS INTEGRALES LTDA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.849.480-0</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3926.9</v>
+        <v>8061.26</v>
       </c>
     </row>
     <row r="211">
@@ -13772,7 +13768,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>707409-47-CM26</t>
+          <t>720-123-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13797,12 +13793,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13812,28 +13808,32 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRALES LTDA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.849.480-0</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>8061.26</v>
+        <v>3926.9</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>720-120-CM26</t>
+          <t>1966-3-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13853,17 +13853,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -13892,13 +13892,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>5465.39</v>
+        <v>791.49</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1966-3-CM26</t>
+          <t>720-120-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13918,17 +13918,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13938,12 +13938,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -13957,7 +13957,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>791.49</v>
+        <v>5465.39</v>
       </c>
     </row>
     <row r="215">
@@ -14849,7 +14849,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1079596-105-CM26</t>
+          <t>1079596-108-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14889,17 +14889,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -14908,13 +14908,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>9535.48</v>
+        <v>3897.74</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1079596-108-CM26</t>
+          <t>1079596-105-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14954,17 +14954,17 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3897.74</v>
+        <v>9535.48</v>
       </c>
     </row>
     <row r="231">
@@ -15044,7 +15044,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>635-737-CM26</t>
+          <t>5702-438-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15084,32 +15084,28 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2969.17</v>
+        <v>1751.4</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>5702-438-CM26</t>
+          <t>635-737-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15134,12 +15130,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15149,28 +15145,32 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1751.4</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1079596-111-CM26</t>
+          <t>1075963-7938-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15195,12 +15195,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15210,12 +15210,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K234" t="inlineStr"/>
@@ -15225,13 +15225,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1196.74</v>
+        <v>1633.21</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1075963-7938-CM26</t>
+          <t>1079596-111-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15256,12 +15256,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15271,12 +15271,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K235" t="inlineStr"/>
@@ -15286,13 +15286,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1633.21</v>
+        <v>1196.74</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>720-164-CM26</t>
+          <t>635-823-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15351,13 +15351,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3070.89</v>
+        <v>1688.26</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>635-823-CM26</t>
+          <t>720-164-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1688.26</v>
+        <v>3070.89</v>
       </c>
     </row>
     <row r="238">
@@ -16190,7 +16190,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1272219-36-CM26</t>
+          <t>1272219-37-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16230,12 +16230,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K250" t="inlineStr"/>
@@ -16245,13 +16245,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1034.72</v>
+        <v>2235.95</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1272219-37-CM26</t>
+          <t>1272219-36-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16291,12 +16291,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -16306,7 +16306,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2235.95</v>
+        <v>1034.72</v>
       </c>
     </row>
     <row r="252">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -17653,7 +17653,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -17819,6 +17819,628 @@
       </c>
       <c r="M275" s="2" t="n">
         <v>4048.99</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>5192-30-CM26</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Equilibrium SpA</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="n">
+        <v>819.9</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>3459-261-CM26</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>65.287.570-K</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Equilibrium SpA</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="n">
+        <v>844.99</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>635-1421-CM26</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>61.606.000-7</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="n">
+        <v>2173.19</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>1236-207-CM26</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>9.454.737-7</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="n">
+        <v>1119.96</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>1075963-13311-CM26</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>tecnopapel s.a.</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="n">
+        <v>6401.54</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>3185-131-CM26</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>61.102.001-5</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="n">
+        <v>1507.39</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>5360-266-CM26</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>CADAQUES SPA</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>77.714.552-5</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="n">
+        <v>8163.86</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>5360-282-CM26</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>70.770.800-k</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>JIREH INFORMATICA Y SERVICIOS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>77.096.320-6</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="n">
+        <v>5117.95</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>1075963-13751-CM26</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="n">
+        <v>4084.39</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>5642-131-CM26</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>61.979.240-8</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Equilibrium SpA</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="n">
+        <v>770.84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M285"/>
+  <dimension ref="A1:M286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9480,7 +9480,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>4232-9-CM26</t>
+          <t>1250331-4-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9520,32 +9520,28 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.478.731-5</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3695.64</v>
+        <v>3730.92</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1250331-4-CM26</t>
+          <t>4232-9-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9570,12 +9566,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9585,22 +9581,26 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
+          <t>77.823.479-3</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>3730.92</v>
+        <v>3695.64</v>
       </c>
     </row>
     <row r="146">
@@ -9923,7 +9923,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1110404-66-CM26</t>
+          <t>1110404-63-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9978,13 +9978,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>5861.48</v>
+        <v>68749.05</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1110404-64-CM26</t>
+          <t>1110404-66-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10024,32 +10024,28 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>28273.64</v>
+        <v>5861.48</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1110404-63-CM26</t>
+          <t>1110404-64-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10089,22 +10085,26 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>68749.05</v>
+        <v>28273.64</v>
       </c>
     </row>
     <row r="154">
@@ -10175,7 +10175,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1236-7-CM26</t>
+          <t>635-109-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10234,13 +10234,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2876.79</v>
+        <v>15116.44</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>635-109-CM26</t>
+          <t>1236-7-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10265,12 +10265,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10280,12 +10280,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10299,7 +10299,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>15116.44</v>
+        <v>2876.79</v>
       </c>
     </row>
     <row r="157">
@@ -10370,7 +10370,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5358-28-CM26</t>
+          <t>1075963-2231-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10390,17 +10390,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA NENE SPA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>76.067.436-2</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10425,13 +10425,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>7524.58</v>
+        <v>3325.8</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1075963-2231-CM26</t>
+          <t>5358-28-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10451,17 +10451,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DISTRIBUIDORA NENE SPA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.067.436-2</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3325.8</v>
+        <v>7524.58</v>
       </c>
     </row>
     <row r="160">
@@ -10679,7 +10679,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1075963-2435-CM26</t>
+          <t>1075963-2443-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10719,22 +10719,26 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1755.9</v>
+        <v>5729.75</v>
       </c>
     </row>
     <row r="164">
@@ -10801,7 +10805,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1075963-2443-CM26</t>
+          <t>1075963-2435-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10841,26 +10845,22 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>5729.75</v>
+        <v>1755.9</v>
       </c>
     </row>
     <row r="166">
@@ -12138,7 +12138,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1272219-13-CM26</t>
+          <t>1272219-12-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12178,28 +12178,32 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1056.64</v>
+        <v>3198.85</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1272219-12-CM26</t>
+          <t>1272219-13-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12239,32 +12243,28 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>16.770.707-6</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3198.85</v>
+        <v>1056.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3390-131-CM26</t>
+          <t>3390-126-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12304,22 +12304,26 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1427.86</v>
+        <v>1157.01</v>
       </c>
     </row>
     <row r="189">
@@ -12390,7 +12394,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3390-126-CM26</t>
+          <t>3390-131-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12430,32 +12434,28 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1157.01</v>
+        <v>1427.86</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>837-217-CM26</t>
+          <t>837-219-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1127.78</v>
+        <v>966.72</v>
       </c>
     </row>
     <row r="192">
@@ -12577,7 +12577,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>837-219-CM26</t>
+          <t>837-218-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t xml:space="preserve">Distribuidora Colon </t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.176.425-k</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12632,13 +12632,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>966.72</v>
+        <v>1417.83</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>837-218-CM26</t>
+          <t>837-217-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distribuidora Colon </t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.176.425-k</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12693,13 +12693,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1417.83</v>
+        <v>1127.78</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>837-214-CM26</t>
+          <t>837-226-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -12739,28 +12739,32 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>GRUPO NUVIX SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+          <t>78.209.441-6</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1147.28</v>
+        <v>870.09</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>837-222-CM26</t>
+          <t>837-224-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12819,13 +12823,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1006.71</v>
+        <v>815.71</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>837-224-CM26</t>
+          <t>837-222-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12884,13 +12888,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>815.71</v>
+        <v>1006.71</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>837-226-CM26</t>
+          <t>837-214-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12910,7 +12914,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -12930,26 +12934,22 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>GRUPO NUVIX SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>78.209.441-6</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>870.09</v>
+        <v>1147.28</v>
       </c>
     </row>
     <row r="199">
@@ -13016,7 +13016,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1151549-88-CM26</t>
+          <t>5702-274-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13036,17 +13036,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13056,28 +13056,32 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Bastian Ignacio</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.027.029-4</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr"/>
+          <t>77.621.112-5</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2621.13</v>
+        <v>1483.14</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1151549-89-CM26</t>
+          <t>5702-273-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13102,12 +13106,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>53.333.710-4</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13117,32 +13121,28 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.478.731-5</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>5075.95</v>
+        <v>913.51</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5702-273-CM26</t>
+          <t>1151549-89-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13167,12 +13167,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13182,28 +13182,32 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>913.51</v>
+        <v>5075.95</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5702-274-CM26</t>
+          <t>1151549-88-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13223,17 +13227,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>53.333.710-4</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA ESTATAL REGIÓN ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13243,26 +13247,22 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>Bastian Ignacio</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.027.029-4</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1483.14</v>
+        <v>2621.13</v>
       </c>
     </row>
     <row r="204">
@@ -13463,7 +13463,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>720-100-CM26</t>
+          <t>2585-309-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>9.454.737-7</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13518,13 +13518,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2546.08</v>
+        <v>2648.6</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2585-309-CM26</t>
+          <t>720-100-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13564,12 +13564,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>ANDRO DAVID LAFUENTE FERNÁNDEZ</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>9.454.737-7</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2648.6</v>
+        <v>2546.08</v>
       </c>
     </row>
     <row r="209">
@@ -13707,7 +13707,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1075963-6178-CM26</t>
+          <t>720-123-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13732,12 +13732,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13747,28 +13747,32 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>12735.33</v>
+        <v>3926.9</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>720-123-CM26</t>
+          <t>1075963-6178-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13793,12 +13797,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13808,32 +13812,28 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>3926.9</v>
+        <v>12735.33</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1966-3-CM26</t>
+          <t>720-120-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13853,17 +13853,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -13892,13 +13892,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>791.49</v>
+        <v>5465.39</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>720-120-CM26</t>
+          <t>1966-3-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13918,17 +13918,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13938,12 +13938,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -13957,7 +13957,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>5465.39</v>
+        <v>791.49</v>
       </c>
     </row>
     <row r="215">
@@ -14349,7 +14349,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1272219-20-CM26</t>
+          <t>1075963-7121-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -14404,13 +14404,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2199.42</v>
+        <v>1143.73</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1075963-7121-CM26</t>
+          <t>1272219-20-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14435,12 +14435,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>76.478.731-5</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1143.73</v>
+        <v>2199.42</v>
       </c>
     </row>
     <row r="223">
@@ -14849,7 +14849,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1079596-108-CM26</t>
+          <t>1079596-105-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14889,17 +14889,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -14908,13 +14908,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3897.74</v>
+        <v>9535.48</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1079596-105-CM26</t>
+          <t>1079596-108-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14954,17 +14954,17 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>9535.48</v>
+        <v>3897.74</v>
       </c>
     </row>
     <row r="231">
@@ -15044,7 +15044,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>5702-438-CM26</t>
+          <t>635-737-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.000-7</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15084,28 +15084,32 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K232" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1751.4</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>635-737-CM26</t>
+          <t>5702-438-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15130,12 +15134,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.606.000-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE ARICA Y PARINACOTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15145,26 +15149,22 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2969.17</v>
+        <v>1751.4</v>
       </c>
     </row>
     <row r="234">
@@ -15422,7 +15422,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2585-580-CM26</t>
+          <t>1075963-8214-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15447,12 +15447,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15462,17 +15462,17 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -15481,13 +15481,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>26292</v>
+        <v>5282.82</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1075963-8214-CM26</t>
+          <t>2585-580-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15512,12 +15512,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15527,17 +15527,17 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5282.82</v>
+        <v>26292</v>
       </c>
     </row>
     <row r="240">
@@ -15617,7 +15617,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3390-257-CM26</t>
+          <t>3390-246-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15676,13 +15676,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1158.46</v>
+        <v>4392.27</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>3390-246-CM26</t>
+          <t>3390-245-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15741,13 +15741,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4392.27</v>
+        <v>4782.94</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3390-245-CM26</t>
+          <t>3390-257-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>4782.94</v>
+        <v>1158.46</v>
       </c>
     </row>
     <row r="244">
@@ -16312,7 +16312,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3459-192-CM26</t>
+          <t>1075963-9655-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16337,12 +16337,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16352,28 +16352,32 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3518.66</v>
+        <v>5202.92</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1075963-9655-CM26</t>
+          <t>3459-192-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16398,12 +16402,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16413,26 +16417,22 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>5202.92</v>
+        <v>3518.66</v>
       </c>
     </row>
     <row r="254">
@@ -16686,7 +16686,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1347870-118-CM26</t>
+          <t>1347870-117-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16751,7 +16751,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1347870-117-CM26</t>
+          <t>1347870-118-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16877,7 +16877,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>720-253-CM26</t>
+          <t>1075963-10940-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16897,17 +16897,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16917,32 +16917,28 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.075.072-7</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>851.02</v>
+        <v>5237.66</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1075963-10940-CM26</t>
+          <t>720-253-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16962,17 +16958,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16982,22 +16978,26 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>5237.66</v>
+        <v>851.02</v>
       </c>
     </row>
     <row r="263">
@@ -17698,7 +17698,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>3459-254-CM26</t>
+          <t>1075963-12750-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17718,17 +17718,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17738,28 +17738,32 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>886.09</v>
+        <v>4048.99</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1075963-12750-CM26</t>
+          <t>3459-254-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17779,17 +17783,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17799,26 +17803,22 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>4048.99</v>
+        <v>886.09</v>
       </c>
     </row>
     <row r="276">
@@ -18072,7 +18072,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1075963-13311-CM26</t>
+          <t>3185-131-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18092,17 +18092,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18112,12 +18112,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>tecnopapel s.a.</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>76.075.072-7</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
@@ -18127,13 +18127,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>6401.54</v>
+        <v>1507.39</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3185-131-CM26</t>
+          <t>1075963-13311-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18153,17 +18153,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18173,12 +18173,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>tecnopapel s.a.</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.075.072-7</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -18188,7 +18188,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1507.39</v>
+        <v>6401.54</v>
       </c>
     </row>
     <row r="282">
@@ -18320,7 +18320,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1075963-13751-CM26</t>
+          <t>3390-412-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18345,12 +18345,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18360,17 +18360,17 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18379,7 +18379,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4084.39</v>
+        <v>1910.32</v>
       </c>
     </row>
     <row r="285">
@@ -18441,6 +18441,71 @@
       </c>
       <c r="M285" s="2" t="n">
         <v>770.84</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>1075963-13751-CM26</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>61.606.001-5</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="n">
+        <v>4084.39</v>
       </c>
     </row>
   </sheetData>
